--- a/doc/fitlog 기능요구서.xlsx
+++ b/doc/fitlog 기능요구서.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\project\ScratchPaper_feature_ui_doc\ScratchPaper\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B64E67-842A-4BB5-A915-C7A349DABF8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDDAFD37-1D92-455A-9B92-9DE6C8B6BBC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{06487F79-C12E-4F1A-B6C2-26058A5623E8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="170">
   <si>
     <t>No</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -94,10 +94,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>issue#</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>김경수</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -126,22 +122,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1. default는 홈 화면 (앱 실행 시)
-2. 로그인 된 상태에서만 출력
-3. 홈 / 커뮤니티 / 지도 / 마이페이지로 구성
-4. 각 버튼 클릭 시 연결된 페이지로 이동
-5. 페이지 탭은 항상 맨 위에 표시됨
-6. 현재 표시중인 페이지는 버튼 색상이 변경 (현재 탭 임을 표시함)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 홈 화면 / 커뮤니티 화면 에서만 표시
-2. 버튼 클릭 시 신규 작성 창으로 이동
-3. 홈 화면 표시 중에 클릭되면 신규 게시글 작성으로 이동됨
-4. 커뮤니티 화면 표시 중에 클릭되면 신규 커뮤니티 추가로 이동됨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>게시글 타이틀</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -154,49 +134,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>게시글 정렬은 내림차 순으로 처리
-1차 : 좋아요 숫자
-2차 댓글 숫자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>필터 설정에 따라 필터링 된 게시글 목록을 제공
-1. 인기탭 : 좋아요 와 댓글 숫자가 많은 게시글 순서로 내림차순 정렬
-2. 내 관심 : 내가 좋아요 (is_like = True) 한 게시글만 모아서 표시
-3. 카테고리 : 카테고리에 따라 게시글을 묶어서 표시 or 해당 탭에 카테고리 필터 제공 (어떤 카테고리가 위에 올라오는게 싫으면)
-4. 최신 : 게시글을 마지막 수정 날짜 순으로 갱신 (수정하면 위로 올라옴)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게시글 (card)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>게시글 목록</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1. 최대 스크롤 개수 있을건지
-2. 데이터 한번에 로딩할지 아니면 일정 개수 단위로 끊어서 요청할지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게시글 목록 표시 영역
-1. 상하 스크롤 (스크롤바 표시 안함)
-2. 목록 중 특정 post 클릭 시 해당 포스트 화면으로 이동함</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>게시글 공유</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>게시글에서 공유 버튼 눌렀을 때 공유 대상을 고르는 플로팅 창 표시
- -&gt; 해당 게시글의 url을 복사해서 지정한 app으로 텍스트 전달
- -&gt; 해당 앱의 입력 창에 url 입력된 상태로?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>공유 시 사용되는 api 가 있을 것으로 추정됨</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -205,36 +150,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>게시글 상세 타이틀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. " &lt; 게시글 " 로 창 타이틀 표시
-2. 게시글 상세 창은 게시글 작성 / 게시글 수정 시 공용으로 사용됨
- -&gt; 다른 용도로 사용 시 "게시글 작성" "게시글 수정" 으로 표시내용 변경</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게시글 표시 / 게시글 작성 / 게시글 수정 공용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게시글 상세 이미지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이미지 여부에 따라 표시 &gt; 없으면 표시 안함 표시내용 크기 가변</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게시글 상세 작성자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게시글 상세 수정일</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>해당 게시글 마지막 수정 날짜 표시</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -243,14 +158,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>게시글 상세 제목</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게시글 상세 내용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2포인트 정도 크게 표시 / bold 채로 굵게</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -267,99 +174,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>데이터에 따라 게시글 카드 표시
-1. 이미지에 따라 카드 크기 가변
-2. 내용의 길이에 따라 카드 크기 가변
-3. 제목과 내용의 최대 표시 글자 수 지정 (실제 글자수와 달리 리스트 표시 글자 수)
-4. 좋아요 / 공유 / 댓글 버튼에 커서 올라가 있으면 강조 (모바일 환경 고려해야 하나?)
-5. 표시 글자 수 넘기면 … 으로 표시함</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게시글 상세 좋아요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>내가 해당 게시글에 좋아요 한 상태 표시
-해당 게시글의 좋아요 개수 표시
-게시글의 좋아요 버튼 클릭 시 내 좋아요 상태 변경 (default = False)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게시글 상세 댓글(목록)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 게시글 이미지
-2. 게시글 작성자 정보 (이름, 아이콘)
-3. 게시글 갱신 일자
-4. 게시글 제목
-5. 게시글 내용
-6. 좋아요 
-7. 좋아요 숫자 증감 표시
-8. 댓글
-9. 댓글 숫자 표시 (협의 필요)
-10. 공유
-11. 카테고리 표시
-12. 게시글 수정 버튼 (협의 필요 - 작성자만 수정 가능)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 해당 게시글의 댓글 개수 표시
-2. 각 댓글의 아이콘 / 이름 / 수정일자를 표시
-3. 댓글 내용 표시 (최대 글자 수 있어야 함)
-4. 댓글은 리스트로 제공
-5. 각 댓글에는 수정(edit) 버튼이 존재
- -&gt; 댓글 수정은 해당 댓글 작성자만 가능
- -&gt; 댓글 수정 시 댓글 입력 매뉴 변경</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게시글 상세 댓글 입력</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게시글 상세 편집</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게시글 상세 댓글 편집</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 입력내용 없을 시 약하게 "댓글을 입력하세요" 출력
-2. 입력내용 없을 시 입력 버튼 비활성화
-3. 입력내용이 있으면 입력 버튼 활성화
-4. 입력 최대 글자 수 필요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 수정 시 입력창 바로 위에 수정할 댓글 내용 붙여서 표시 (입력창 위 확장)
-2. 내용 변경이 없으면 (동일하면) 입력버튼 클릭 불가
-3. x 버튼으로 수정모드에서 원래대로 돌아가는 기능 제공해야 함</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>클릭 시 플로트 메뉴 표시 
-1. 수정 : 게시글 수청 화면으로 이동
-2. 삭제 : 게시글 삭제 여부 확인 팝업 호출 &gt; 확인 시 게시글 삭제, 화면은 홈 화면으로 이동</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>게시글 작성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게시글 작성 제목</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게시글 작성 타이틀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>타이틀을 "게시글 상세"로 표시 
-해당 영역 클릭 시 직전에 보고 있던 창으로 이동 (검토 필요)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -368,23 +183,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>게시글 작성 내용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게시글 작성 카테고리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>카테고리 선택을 버튼 메뉴로 제공
 기본 선택 상태 제공 (무조건 값을 가져야 함)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>게시글 작성 위치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>특정 위치를 데이터로 등록
 위치를 신규 등록하거나 수정할 때 위치 찾아서 등록하는 기능 활용</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -394,64 +197,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>게시글 작성 이미지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>해당 게시글에서 표시할 이미지 등록
 1개의 이미지만 등록 가능</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>게시글 작성 submit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>게시글 수정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>게시글 수정 타이틀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게시글을 등록하는 버튼
-아래 조건을 만족하는 경우만 등록 버튼 클릭 가능
-1) 제목
-2) 내용
-3) 카테고리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>타이틀 제목이 "게시글 수정" 으로 표시</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게시글 수정 내용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>제목 ~ 이미지 까지 작성 내용 전부 비교
-작성된 내용 중 변경 사항이 있는지 체크해야 함 &gt; 변경사항이 있는 경우만 submit 버튼 클릭 가능함</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>지도</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>지도 타이틀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>지도 맵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>지도 마커들</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>지도 줌인</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -468,15 +226,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>마커 클릭 시 툴팁 플로팅 창 출력 (아래 정보 표시)
-1. 카테고리 / 분류 (게시글 or 커뮤니티)
-2. 제목
-3. 내용
-4. 위치
-5. 상세보기 (커뮤니티/게시글) : 클릭 시 해당 화면으로 이동</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"지도" 표시</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -490,14 +239,6 @@
   </si>
   <si>
     <t>게시글 / 커뮤니티 중에서 위치 좌표를 가지고 있는 것들을 표시</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>지도 현재 표시위치에 따라 동적으로 읽어오는 것으로 검토</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>확대율은 10  ~ 20% 사이로 생각 중</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -515,6 +256,491 @@
   <si>
     <t>화면 포커스 변경
  -&gt; 화면 이동 시 연출 필요한지?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sub2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버튼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버튼은 4개로 구성 (홈/카테고리/지도/마이페이지)
+각 버튼 클릭 시 해당 페이지로 이동
+해당 페이지 버튼 True (나머진 False)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>앱 실행 시 &lt;홈&gt; 버튼 선택 상태로 표시
+로그인 상태에서만 보여준다.
+표시위치는 화면 하단에 고정 (중앙하단 anchor)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>표시조건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버튼동작 (홈)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>커뮤니티 화면 표시 중에 클릭되면 신규 커뮤니티 추가로 이동됨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>홈 화면 표시 중에 클릭되면 신규 게시글 작성으로 이동됨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>홈 / 커뮤니티 화면 에서만 표시
+표시 위치는 우측 하단</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우측 하단 표시 수정 검토
+(게시판이나 커뮤니티 참여 버튼 입력에 방해될 수도 있음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카테고리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동작</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필터는 동시에 1개만 선택 가능
+선택된 필터는 활성화 표시
+default는 인기탭
+게시글 정렬은 좋아요 내림차순 표시함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인기 : 모든 글 표시
+관심 : 내가 관심 선택한 카테고리만
+카테고리 : 특정 카테고리만 표시
+최신 : 갱신일자가 빠른 순서대로 표시 (정렬 변경)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이미지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게시글의 이미지 URL 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작성자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름 / 아이콘 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>갱신일자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게시글 데이터 갱신일자 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제목</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게시글 제목 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게시글 내용 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋아요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게시글의 좋아요 숫자 표시 / 내 좋아요 설정 여부 표시 (on/off)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>댓글</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게시글의 댓글 숫자 표시
+클릭 시 게시글 상세보기로 이동 -&gt; 댓글 입력창에 포커스 간 상태로 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>클릭 시 공유 플로팅 창 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게시글의 카테고리 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>편집</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게시글 데이터 편집 버튼 / 작성자만 클릭 가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>표시 글자 제한 있음 / 넘어가면 뒤를 … 으로 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이터 없으면 이미지 없는 상태로 표시함 
+(해당 공간이 줄어듬)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hover 시 아이콘 크기 증가 (포커스 여부 표시)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작성자인지 검증 부분 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상하 스크롤 (스크롤바 표시 안함)
+카드 클릭 시 해당 포스트 상세보기로 이동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정 개수 단위로 끊어서 요청해야 함
+스크롤 발생 시 추가 로딩
+최초 로딩할 때 어디 부분 표시해야 하는지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공유버튼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공유플로팅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게시글에서 공유 버튼 눌렀을 때 공유 대상을 고르는 플로팅 창 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>app을 지정하면 해당 게시글의 url을 복사해서 지정한 app으로 전달</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭘 전달해서 공유하는지는 모름 &gt; 할꺼면 조사 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타이틀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수정일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>댓글 목록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>댓글 입력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"게시글"로 고정 문구 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>등록된 이미지 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이미지 없으면 해당 공간 없애고 나머지 내용 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋아요 상태 표시 / 클릭 시 좋아요 상태 변경
+좋아요 개수 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플로트메뉴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삭제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>클릭 시 게시글 수청 화면으로 이동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>클릭 시 팝업 화면 출력 &gt; 팝업에서 확인 누르면 게시글 삭제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>표시할 게시글이 없으면 홈 화면으로 이동함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">클릭 시 플로트 메뉴 표시 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>헤더</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작성자 정보</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>댓글 내용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>댓글(item)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스크롤 발생 시 동적 로딩 기능 고려</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게시글(item)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>댓글 개수 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마지막 수정일 기준으로 내림차순 표시 / 스크롤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>댓글 작성자 아이콘, 이름 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작성된 댓글 내용 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>댓글 작성자만 편집 가능 / 클릭 시 플로팅 메뉴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>편집메뉴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>댓글 편집 / 삭제 여부 선택 매뉴 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>편집(edit)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버튼동작(커뮤니티)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입력내용이 있으면 입력 버튼 활성화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>submit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>input</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입력 최대 글자 수 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입력내용 없을 시 약하게 "댓글을 입력하세요" 출력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>댓글 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수정할 댓글 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수정할 댓글 1개를 타겟으로 해서 입력창 바로 위에 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지금 수정할 댓글 1개를 타겟으로 표시할 수 있어야 함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입력창 바로 위에 수정할 댓글 내용 붙여서 표시 (입력창 위 확장)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>취소(x)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내용 변경 없으면 클릭불가 (비교 체크 필요)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수정할 댓글 내용 택스트로 입력된 상태로 제공해야 함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수정 모드를 취소하고 원래 상태로 돌림</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신규 개시글</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제목 / 내용 / 카테고리 필수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게시글을 등록하는 버튼
+필수 입력 값들이 있어야 입력 가능 (not null)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타이틀을 "게시글 상세"로 표시 
+해당 영역 클릭 시 직전에 보고 있던 창으로 이동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타이틀 제목이 "게시글 수정" 으로 표시
+해당 영역 클릭 시 직전에 보고 있던 창으로 이동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제목 입력되어 있음
+입력된 글자수 / 최대 글자수 표시해줌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내용 입력되어 있음
+입력된 글자수 / 최대 글자수 표시해줌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카테고리 선택되어 있음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위치 정보 원래 게시글하고 동일하게 설정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게시글 작성 UX를 서로 공유함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이미지 원래 게시글하고 동일하게 설정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이전 게시글의 내용에서 변경 사항 없으면 클릭 불가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>맵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마커</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지도 현재 표시위치에 따라 동적으로 읽어오는 것으로 검토
+지도위치 변경 시 동적으로 읽어와야 함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>확대율은 10  ~ 20% 사이로 생각 중인데 실제 지도앱은 세계지도 레벨까지 확대됨 (검토 필요)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마커 클릭 시 툴팁 플로팅 창 출력해서 해당 마커의 정보 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상세 정보창은 동시에 1개만 열 수 있음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상세보기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게시글의 제목 표시</t>
+  </si>
+  <si>
+    <t>게시글의 내용 표시</t>
+  </si>
+  <si>
+    <t>게시글의 위치 표시</t>
+  </si>
+  <si>
+    <t>해당 게시글 상세 창으로 이동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>커뮤니티 개발 시 해당 기능 같이 이용 (표시 구분은 필요)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>커뮤니티의 마커인 경우 커뮤니티 상세 창으로 이동</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -576,7 +802,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -592,7 +818,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -929,19 +1158,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F39685BB-7022-4C5F-9511-197EEAB9365B}">
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="7.5625" style="4" customWidth="1"/>
     <col min="2" max="2" width="15.9375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="22.25" style="4" customWidth="1"/>
-    <col min="4" max="4" width="9.25" style="4" customWidth="1"/>
+    <col min="3" max="4" width="22.25" style="4" customWidth="1"/>
     <col min="5" max="5" width="64.1875" style="3" customWidth="1"/>
     <col min="6" max="6" width="11.3125" style="4" customWidth="1"/>
     <col min="7" max="7" width="10.4375" style="4" customWidth="1"/>
     <col min="8" max="8" width="8.25" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.4375" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="37.875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="50.4375" style="3" customWidth="1"/>
     <col min="11" max="12" width="8.25" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -956,9 +1184,9 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -973,7 +1201,7 @@
       <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -988,7 +1216,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
@@ -1003,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>9</v>
@@ -1026,7 +1254,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
@@ -1041,13 +1269,13 @@
         <v>10</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>9</v>
@@ -1059,33 +1287,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="135" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:12" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>9</v>
@@ -1097,33 +1325,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="67.5" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:12" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>9</v>
@@ -1135,36 +1363,36 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>25</v>
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>9</v>
@@ -1173,83 +1401,55 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="101.25" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="202.5" x14ac:dyDescent="0.6">
+        <v>62</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>9</v>
+        <v>129</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="50.65" x14ac:dyDescent="0.6">
+        <v>61</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1257,28 +1457,28 @@
         <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>9</v>
@@ -1287,37 +1487,35 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="50.65" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:12" ht="67.5" x14ac:dyDescent="0.6">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>9</v>
+      <c r="C10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>35</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="J10" s="2"/>
       <c r="K10" s="1" t="s">
         <v>9</v>
       </c>
@@ -1325,37 +1523,35 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="85.9" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:12" ht="67.5" x14ac:dyDescent="0.6">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>9</v>
+      <c r="B11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>39</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="J11" s="2"/>
       <c r="K11" s="1" t="s">
         <v>9</v>
       </c>
@@ -1363,35 +1559,37 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>9</v>
+      <c r="B12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>89</v>
+      </c>
       <c r="K12" s="1" t="s">
         <v>9</v>
       </c>
@@ -1403,29 +1601,29 @@
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>9</v>
+      <c r="B13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="1" t="s">
@@ -1439,29 +1637,29 @@
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>9</v>
+      <c r="B14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="1" t="s">
@@ -1475,32 +1673,32 @@
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>9</v>
+      <c r="B15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>9</v>
@@ -1513,32 +1711,32 @@
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>9</v>
+      <c r="B16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>9</v>
@@ -1547,35 +1745,37 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="50.65" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>9</v>
+      <c r="B17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="K17" s="1" t="s">
         <v>9</v>
       </c>
@@ -1583,35 +1783,37 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="67.5" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>9</v>
+      <c r="B18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="K18" s="1" t="s">
         <v>9</v>
       </c>
@@ -1619,35 +1821,37 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="118.15" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>9</v>
+      <c r="B19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="K19" s="1" t="s">
         <v>9</v>
       </c>
@@ -1655,33 +1859,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="67.5" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>9</v>
+      <c r="B20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="1" t="s">
@@ -1691,35 +1895,37 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="50.65" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>9</v>
+      <c r="B21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>91</v>
+      </c>
       <c r="K21" s="1" t="s">
         <v>9</v>
       </c>
@@ -1727,35 +1933,37 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:12" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>9</v>
+        <v>92</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="K22" s="1" t="s">
         <v>9</v>
       </c>
@@ -1763,35 +1971,37 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="K23" s="1" t="s">
         <v>9</v>
       </c>
@@ -1799,35 +2009,37 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>99</v>
+      </c>
       <c r="K24" s="1" t="s">
         <v>9</v>
       </c>
@@ -1835,33 +2047,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="1" t="s">
@@ -1871,36 +2083,36 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>9</v>
@@ -1909,33 +2121,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A27" s="1">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="1" t="s">
@@ -1945,33 +2157,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="84.4" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A28" s="1">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="1" t="s">
@@ -1986,30 +2198,32 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J29" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="K29" s="1" t="s">
         <v>9</v>
       </c>
@@ -2017,35 +2231,37 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="50.65" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A30" s="1">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J30" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="K30" s="1" t="s">
         <v>9</v>
       </c>
@@ -2053,33 +2269,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A31" s="1">
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="1" t="s">
@@ -2089,37 +2305,35 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A32" s="1">
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>86</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>9</v>
+        <v>108</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>95</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="J32" s="2"/>
       <c r="K32" s="1" t="s">
         <v>9</v>
       </c>
@@ -2127,109 +2341,99 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A33" s="1">
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>9</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="J33" s="2"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A34" s="1">
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>9</v>
+        <v>110</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>9</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A35" s="1">
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>9</v>
+        <v>115</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="1" t="s">
@@ -2239,77 +2443,1341 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A36" s="1">
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>9</v>
+        <v>102</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="101.25" x14ac:dyDescent="0.6">
+        <v>119</v>
+      </c>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A37" s="1">
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>9</v>
+        <v>116</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J37" s="2"/>
-      <c r="K37" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L37" s="1" t="s">
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J38" s="2"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J39" s="2"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J40" s="2"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A43" s="1">
+        <v>41</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J43" s="2"/>
+      <c r="K43" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J45" s="2"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J46" s="2"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J47" s="2"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+    </row>
+    <row r="48" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A48" s="1">
+        <v>42</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J48" s="2"/>
+      <c r="K48" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A49" s="1">
+        <v>43</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J49" s="2"/>
+      <c r="K49" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A50" s="1">
+        <v>44</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J50" s="2"/>
+      <c r="K50" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A51" s="1">
+        <v>45</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J51" s="2"/>
+      <c r="K51" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A52" s="1">
+        <v>46</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A53" s="1">
+        <v>47</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J53" s="2"/>
+      <c r="K53" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A54" s="1">
+        <v>48</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A55" s="1">
+        <v>49</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A56" s="1">
+        <v>43</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J56" s="2"/>
+      <c r="K56" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A57" s="1">
+        <v>44</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J57" s="2"/>
+      <c r="K57" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A58" s="1">
+        <v>45</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J58" s="2"/>
+      <c r="K58" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A59" s="1">
+        <v>46</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A60" s="1">
+        <v>47</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J60" s="2"/>
+      <c r="K60" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A61" s="1">
+        <v>48</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J61" s="2"/>
+      <c r="K61" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A62" s="1">
+        <v>51</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J62" s="2"/>
+      <c r="K62" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A63" s="1">
+        <v>52</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A64" s="1">
+        <v>53</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A65" s="1">
+        <v>54</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A66" s="1">
+        <v>55</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J66" s="2"/>
+      <c r="K66" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A67" s="1">
+        <v>56</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A68" s="1">
+        <v>57</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A69" s="1">
+        <v>57</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A70" s="1">
+        <v>57</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J70" s="2"/>
+      <c r="K70" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A71" s="1">
+        <v>57</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J71" s="2"/>
+      <c r="K71" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A72" s="1">
+        <v>57</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J72" s="2"/>
+      <c r="K72" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A73" s="1">
+        <v>57</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L73" s="1" t="s">
         <v>9</v>
       </c>
     </row>
